--- a/Resultado_Atualizacao_AutoInspecao.xlsx
+++ b/Resultado_Atualizacao_AutoInspecao.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,12 +442,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0106372-96.2024.8.17.2001</t>
+          <t>0055622-96.2012.8.17.0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -460,12 +460,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0004701-36.2012.8.17.0001</t>
+          <t>0083876-45.2013.8.17.0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0003740-83.2024.8.17.2100</t>
+          <t>0059179-86.2015.8.17.0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,12 +496,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000680-05.2024.8.17.2100</t>
+          <t>0070751-73.2014.8.17.0001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -514,12 +514,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0002125-92.2023.8.17.2100</t>
+          <t>0000923-26.2018.8.17.2110</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000635-39.2015.8.17.0120</t>
+          <t>0000444-66.2019.8.17.2120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0001515-30.2024.8.17.2120</t>
+          <t>0000489-79.2022.8.17.2180</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -568,12 +568,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000611-54.2024.8.17.2170</t>
+          <t>0000096-96.2018.8.17.2180</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -586,12 +586,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000775-19.2024.8.17.2170</t>
+          <t>0000006-54.2019.8.17.2180</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000060-74.2024.8.17.2170</t>
+          <t>0000480-46.2023.8.17.2160</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -622,12 +622,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000571-44.2020.8.17.2160</t>
+          <t>0000055-82.2024.8.17.2160</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -640,12 +640,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000330-39.2022.8.17.2180</t>
+          <t>0000556-56.2019.8.17.2210</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001317-08.2022.8.17.2170</t>
+          <t>0001565-19.2020.8.17.2210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0000261-87.2010.8.17.0220</t>
+          <t>0000385-60.2023.8.17.2210</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001510-44.2022.8.17.2260</t>
+          <t>0001228-79.2024.8.17.2310</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001143-58.2024.8.17.2160</t>
+          <t>0001809-50.2024.8.17.2260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001173-95.2023.8.17.2300</t>
+          <t>0000637-60.2018.8.17.0360</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0000361-89.2018.8.17.2280</t>
+          <t>0002967-43.2024.8.17.2260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -766,12 +766,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0025998-58.2021.8.17.2370</t>
+          <t>0000107-19.2018.8.17.0340</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001273-98.2022.8.17.2360</t>
+          <t>0000148-47.2023.8.17.2300</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001583-15.2023.8.17.4480</t>
+          <t>0002225-86.2022.8.17.2260</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0000336-20.2024.8.17.2360</t>
+          <t>0001472-75.2024.8.17.2320</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0006022-31.2022.8.17.2370</t>
+          <t>0000539-65.2024.8.17.2300</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0004039-60.2024.8.17.2100</t>
+          <t>0022883-58.2023.8.17.2370</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -874,12 +874,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0033573-49.2023.8.17.2370</t>
+          <t>0001000-77.2022.8.17.2180</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0001022-60.2017.8.17.2100</t>
+          <t>0020700-17.2023.8.17.2370</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0000205-41.2001.8.17.0100</t>
+          <t>0000028-25.2023.8.17.2390</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0002256-66.2025.8.17.8221</t>
+          <t>0000085-54.2023.8.17.2160</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0002122-39.2025.8.17.8221</t>
+          <t>0000242-66.2022.8.17.2320</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0001229-82.2024.8.17.8221</t>
+          <t>0000394-06.2019.8.17.2390</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0000566-36.2023.8.17.2380</t>
+          <t>0000053-83.2021.8.17.2430</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1000,12 +1000,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0001213-56.2023.8.17.2210</t>
+          <t>0000481-53.2024.8.17.2400</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1018,12 +1018,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0001860-42.2019.8.17.2420</t>
+          <t>0000133-02.2023.8.17.2390</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0000590-78.2024.8.17.2170</t>
+          <t>0000202-85.2016.8.17.2420</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1054,12 +1054,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0000618-75.2021.8.17.2550</t>
+          <t>0007000-24.2011.8.17.0420</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0027822-52.2021.8.17.2370</t>
+          <t>0001706-15.2016.8.17.0420</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0005898-39.2022.8.17.2470</t>
+          <t>0000134-80.2021.8.17.0280</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0001627-98.2019.8.17.2370</t>
+          <t>0000459-07.2022.8.17.2160</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0004893-45.2023.8.17.2470</t>
+          <t>0008783-84.2019.8.17.2420</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1144,12 +1144,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0000673-38.2024.8.17.5810</t>
+          <t>0001132-69.2024.8.17.2470</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1162,12 +1162,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0016143-45.2023.8.17.2480</t>
+          <t>0000608-05.2024.8.17.2460</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0001990-71.2015.8.17.0480</t>
+          <t>0004703-53.2021.8.17.2470</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1198,12 +1198,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0007962-60.2020.8.17.2480</t>
+          <t>0001414-49.2020.8.17.2470</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0009704-57.2019.8.17.2480</t>
+          <t>0004720-89.2021.8.17.2470</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0014452-64.2021.8.17.2480</t>
+          <t>0000914-68.2024.8.17.2170</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0004437-80.2018.8.17.2370</t>
+          <t>0005241-97.2022.8.17.2470</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1270,12 +1270,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0000835-89.2024.8.17.2170</t>
+          <t>0000067-77.2022.8.17.2480</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0000494-47.2023.8.17.2510</t>
+          <t>0007246-62.2022.8.17.2480</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0001855-79.2024.8.17.2570</t>
+          <t>0013503-36.2015.8.17.0480</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0000331-69.2024.8.17.2110</t>
+          <t>0000462-58.2019.8.17.2550</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0000483-57.2019.8.17.2510</t>
+          <t>0000382-17.2018.8.17.0550</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0038883-36.2023.8.17.2370</t>
+          <t>0011263-73.2024.8.17.2480</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0000874-55.2021.8.17.2570</t>
+          <t>0001014-48.2015.8.17.0550</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0001424-92.2023.8.17.2210</t>
+          <t>0000566-17.2011.8.17.0550</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0000195-82.2016.8.17.2650</t>
+          <t>0000632-55.2015.8.17.0550</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0000410-26.2024.8.17.2570</t>
+          <t>0011263-73.2024.8.17.2480</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0000411-62.2024.8.17.2650</t>
+          <t>0000949-37.2022.8.17.2610</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0002809-46.2024.8.17.2370</t>
+          <t>0000033-37.2021.8.17.2610</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0006269-41.2024.8.17.2370</t>
+          <t>0006399-09.2022.8.17.3370</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0021441-62.2020.8.17.2370</t>
+          <t>0000095-93.2019.8.17.2110</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0034396-62.2019.8.17.2370</t>
+          <t>0000099-07.2020.8.17.2560</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0000136-71.2024.8.17.2470</t>
+          <t>0002217-18.2023.8.17.2570</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0001563-30.2017.8.17.2218</t>
+          <t>0000065-18.2024.8.17.2390</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0000180-74.2020.8.17.2650</t>
+          <t>0018069-17.2024.8.17.3130</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0000104-94.2022.8.17.2160</t>
+          <t>0000147-60.2022.8.17.4640</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0000459-56.2024.8.17.2800</t>
+          <t>0000532-37.2024.8.17.4640</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0000251-06.2015.8.17.0790</t>
+          <t>0003114-37.2023.8.17.2670</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1648,12 +1648,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0000483-62.2008.8.17.0790</t>
+          <t>0001681-54.2024.8.17.2640</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0000593-93.2023.8.17.2420</t>
+          <t>0000067-33.2021.8.17.4640</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0023139-44.2020.8.17.2810</t>
+          <t>0000870-68.2024.8.17.2390</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0000967-40.2022.8.17.2810</t>
+          <t>0004199-24.2024.8.17.2670</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1720,12 +1720,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0002551-36.2020.8.17.2480</t>
+          <t>0000715-65.2016.8.17.0670</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0017356-71.2020.8.17.2810</t>
+          <t>0000534-69.2021.8.17.2390</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0063468-93.2023.8.17.2810</t>
+          <t>0000267-72.2018.8.17.2400</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0004323-97.2024.8.17.2640</t>
+          <t>0002091-28.2021.8.17.8231</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0007908-35.2024.8.17.2810</t>
+          <t>0002102-34.2012.8.17.0710</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0028706-51.2023.8.17.2810</t>
+          <t>0002800-42.2022.8.17.2730</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1828,12 +1828,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0009183-24.2021.8.17.2810</t>
+          <t>0000582-95.2020.8.17.0730</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1846,12 +1846,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0030200-48.2023.8.17.2810</t>
+          <t>0003960-34.2024.8.17.2730</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0000435-47.2021.8.17.2860</t>
+          <t>0000436-34.2021.8.17.2730</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1882,12 +1882,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0000797-38.2014.8.17.0130</t>
+          <t>0008742-44.2017.8.17.2370</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1900,12 +1900,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0000284-22.2019.8.17.2870</t>
+          <t>0001074-42.2018.8.17.2740</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0001785-70.2023.8.17.2320</t>
+          <t>0035349-25.2023.8.17.2810</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1936,12 +1936,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0000269-20.2020.8.17.2320</t>
+          <t>0000095-43.2024.8.17.4980</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0000871-57.2021.8.17.2940</t>
+          <t>0009373-79.2024.8.17.2810</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0000397-81.2024.8.17.2940</t>
+          <t>0000204-97.2024.8.17.3350</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0000040-79.2023.8.17.2021</t>
+          <t>0006385-38.2021.8.17.8227</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2008,12 +2008,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0000113-94.2021.8.17.2870</t>
+          <t>0000434-89.2020.8.17.2830</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2026,12 +2026,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0000775-53.2024.8.17.2870</t>
+          <t>0001904-85.2021.8.17.2260</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0000874-23.2024.8.17.2870</t>
+          <t>0012925-57.2021.8.17.2810</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2062,12 +2062,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0001524-98.2015.8.17.0570</t>
+          <t>0000422-84.2023.8.17.2890</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2080,12 +2080,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0031199-31.2021.8.17.2370</t>
+          <t>0000504-86.2021.8.17.2890</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2098,12 +2098,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0003631-85.2012.8.17.0420</t>
+          <t>0000494-34.2023.8.17.4810</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2116,12 +2116,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0012742-26.2024.8.17.2990</t>
+          <t>0000657-33.2022.8.17.2390</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0016296-66.2024.8.17.2990</t>
+          <t>0000327-86.2019.8.17.2860</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0014283-32.2014.8.17.0990</t>
+          <t>0000156-27.2022.8.17.2860</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0000194-36.2022.8.17.5480</t>
+          <t>0000336-94.2024.8.17.2400</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0011086-35.2015.8.17.0990</t>
+          <t>0000177-73.2023.8.17.2890</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2206,12 +2206,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0000942-08.2017.8.17.1030</t>
+          <t>0000135-43.2018.8.17.2520</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2224,12 +2224,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0000317-52.2021.8.17.2640</t>
+          <t>0000414-26.2015.8.17.0130</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0003695-39.2023.8.17.3030</t>
+          <t>0000184-02.2022.8.17.2890</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2260,12 +2260,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0000049-26.2020.8.17.3030</t>
+          <t>0021963-33.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2278,12 +2278,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0001917-69.2013.8.17.1030</t>
+          <t>0003059-34.2013.8.17.0990</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2296,12 +2296,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0000587-72.2024.8.17.3060</t>
+          <t>0002583-29.2021.8.17.2990</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2314,12 +2314,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0004609-41.2023.8.17.2210</t>
+          <t>0017908-39.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2332,12 +2332,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0000433-16.2012.8.17.1010</t>
+          <t>0008247-36.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0000018-38.2019.8.17.2190</t>
+          <t>0000937-92.2023.8.17.8234</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0000362-16.2022.8.17.3030</t>
+          <t>0000574-15.2024.8.17.2950</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2386,12 +2386,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0001054-73.2022.8.17.2170</t>
+          <t>0000226-02.2021.8.17.2950</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2404,12 +2404,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0012261-97.2023.8.17.2990</t>
+          <t>0015206-92.2013.8.17.0990</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2422,7 +2422,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0037486-21.2019.8.17.2001</t>
+          <t>0002328-83.2023.8.17.2640</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2440,7 +2440,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0002116-62.2023.8.17.2640</t>
+          <t>0011708-16.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0000681-87.2019.8.17.2480</t>
+          <t>0049697-82.2022.8.17.2810</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0004400-54.2024.8.17.3110</t>
+          <t>0028043-05.2023.8.17.2810</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2494,12 +2494,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0000112-66.2023.8.17.4640</t>
+          <t>0023403-22.2024.8.17.2810</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2512,12 +2512,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0000429-95.2023.8.17.3110</t>
+          <t>0001175-91.2018.8.17.0990</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0001006-10.2024.8.17.5480</t>
+          <t>0003234-18.2019.8.17.0990</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2548,12 +2548,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0001583-82.2024.8.17.2280</t>
+          <t>0001557-51.2022.8.17.4480</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0003269-15.2022.8.17.3110</t>
+          <t>0020884-49.2020.8.17.3090</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2584,12 +2584,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0001076-60.2019.8.17.2260</t>
+          <t>0004623-59.2024.8.17.2640</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0003853-17.2011.8.17.1090</t>
+          <t>0007247-46.2008.8.17.0990</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>PARTIDOR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2620,12 +2620,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0034152-69.2022.8.17.2810</t>
+          <t>0000416-34.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0017578-42.2024.8.17.2990</t>
+          <t>0000885-09.2021.8.17.5990</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0000175-32.2016.8.17.1150</t>
+          <t>0031418-90.2022.8.17.2990</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2674,12 +2674,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0000867-31.2024.8.17.2870</t>
+          <t>0020243-31.2024.8.17.2990</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0002122-73.2024.8.17.3080</t>
+          <t>0000759-21.2015.8.17.0670</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2710,12 +2710,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0000520-91.2021.8.17.2970</t>
+          <t>0001556-13.2024.8.17.3020</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2728,12 +2728,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0002411-54.2016.8.17.3090</t>
+          <t>0001380-44.2015.8.17.0920</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2746,12 +2746,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0025055-72.2018.8.17.0001</t>
+          <t>0002998-81.2024.8.17.3030</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2764,7 +2764,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0006935-40.2023.8.17.5001</t>
+          <t>0004650-59.2013.8.17.1110</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0000662-46.2023.8.17.2220</t>
+          <t>0005668-80.2023.8.17.3110</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2800,12 +2800,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0075284-12.2013.8.17.0001</t>
+          <t>0003041-68.2022.8.17.2260</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2818,12 +2818,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0058930-71.2023.8.17.2001</t>
+          <t>0000090-02.2014.8.17.0670</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2836,12 +2836,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0004701-36.2012.8.17.0001</t>
+          <t>0000301-37.2018.8.17.3050</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0018263-44.2014.8.17.0001</t>
+          <t>0003314-19.2022.8.17.3110</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0133136-22.2024.8.17.2001</t>
+          <t>0000486-97.2024.8.17.2910</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2890,12 +2890,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0145994-96.2009.8.17.0001</t>
+          <t>0000546-31.2021.8.17.2860</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2908,12 +2908,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0014988-82.2017.8.17.0001</t>
+          <t>0002201-87.2024.8.17.2260</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2926,12 +2926,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0122082-70.2009.8.17.0001</t>
+          <t>0000242-22.2021.8.17.4480</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PARTIDOR</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2944,12 +2944,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0106372-96.2024.8.17.2001</t>
+          <t>0000505-64.2020.8.17.2160</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0070366-27.2023.8.17.2001</t>
+          <t>0000231-71.2018.8.17.2160</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0007319-76.2024.8.17.3090</t>
+          <t>0004615-65.2014.8.17.1110</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2998,7 +2998,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0033542-71.2021.8.17.3090</t>
+          <t>0011727-47.2023.8.17.3090</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0113460-25.2023.8.17.2001</t>
+          <t>0012311-80.2024.8.17.3090</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3034,12 +3034,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>0005837-17.2023.8.17.2480</t>
+          <t>0002074-48.2023.8.17.8222</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>0008224-68.2018.8.17.3130</t>
+          <t>0003469-35.2023.8.17.2480</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3070,12 +3070,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0007432-83.2017.8.17.2990</t>
+          <t>0000641-08.2024.8.17.3070</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>0014010-31.2014.8.17.0480</t>
+          <t>0001276-23.2023.8.17.5980</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3106,12 +3106,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>0015264-62.2022.8.17.3130</t>
+          <t>0000788-11.2022.8.17.2680</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3124,12 +3124,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>0005950-92.2008.8.17.1090</t>
+          <t>0000282-29.2022.8.17.3070</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>0009477-96.2021.8.17.2480</t>
+          <t>0014356-34.2024.8.17.3130</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3160,12 +3160,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>0075623-10.2022.8.17.2990</t>
+          <t>0018846-44.2005.8.17.0001</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3178,12 +3178,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>0024035-48.2024.8.17.2810</t>
+          <t>0000689-24.2012.8.17.1150</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3196,12 +3196,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>0039579-07.2000.8.17.0001</t>
+          <t>0154921-74.2023.8.17.2001</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3214,12 +3214,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>0084376-47.2021.8.17.2001</t>
+          <t>0003388-39.2023.8.17.3110</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3232,12 +3232,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>0131964-95.2018.8.17.2990</t>
+          <t>0000394-79.2022.8.17.3140</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3250,12 +3250,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>0000827-56.2021.8.17.4001</t>
+          <t>0003212-60.2023.8.17.3110</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0119993-68.2021.8.17.2001</t>
+          <t>0003766-58.2024.8.17.3110</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3286,12 +3286,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>0000319-30.2018.8.17.0990</t>
+          <t>0001081-45.2023.8.17.3100</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3304,12 +3304,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>0008954-57.2018.8.17.0001</t>
+          <t>0000144-69.2021.8.17.2400</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3322,12 +3322,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>0011289-21.2023.8.17.3090</t>
+          <t>0005448-44.2023.8.17.2670</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3340,12 +3340,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>0027165-98.2005.8.17.0001</t>
+          <t>0000117-23.2021.8.17.3100</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3358,12 +3358,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>0052403-79.2018.8.17.2001</t>
+          <t>0000580-71.2021.8.17.3000</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3376,12 +3376,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>0014517-36.2024.8.17.2001</t>
+          <t>0001456-12.2022.8.17.2670</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3394,12 +3394,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>0017949-24.2023.8.17.8201</t>
+          <t>0000429-57.2024.8.17.2400</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3412,12 +3412,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>0009909-72.2023.8.17.8227</t>
+          <t>0020483-56.2022.8.17.3130</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3430,12 +3430,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>0028643-28.2023.8.17.2001</t>
+          <t>0008299-64.2016.8.17.1130</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3448,12 +3448,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>0026129-15.2017.8.17.2001</t>
+          <t>0018952-95.2023.8.17.3130</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3466,12 +3466,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>0020941-70.2019.8.17.2001</t>
+          <t>0013421-45.2019.8.17.0001</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3484,12 +3484,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>0111267-08.2021.8.17.2001</t>
+          <t>0022728-95.2023.8.17.2001</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>0055514-61.2024.8.17.2001</t>
+          <t>0014611-23.2020.8.17.2001</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3520,12 +3520,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>0119370-33.2023.8.17.2001</t>
+          <t>0016038-46.2017.8.17.0001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3538,12 +3538,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>0074674-72.2024.8.17.2001</t>
+          <t>0008081-61.2019.8.17.8201</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3556,12 +3556,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>0027310-07.2024.8.17.2001</t>
+          <t>0000478-79.2008.8.17.0001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3574,12 +3574,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>0024389-75.2024.8.17.2001</t>
+          <t>0015327-56.2008.8.17.0001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3592,12 +3592,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>0044536-41.2006.8.17.0001</t>
+          <t>0041726-93.2006.8.17.0001</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3610,12 +3610,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>0093293-52.1995.8.17.0001</t>
+          <t>0003890-75.2021.8.17.2001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>PARTIDOR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3628,12 +3628,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>0017176-33.2015.8.17.2001</t>
+          <t>0022985-13.2024.8.17.8201</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3646,12 +3646,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>0016510-27.2018.8.17.2001</t>
+          <t>0064540-83.2024.8.17.2001</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3664,12 +3664,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>0032823-29.2019.8.17.2001</t>
+          <t>0118868-60.2024.8.17.2001</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3682,12 +3682,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>0000844-53.2023.8.17.3280</t>
+          <t>0064707-77.2010.8.17.0001</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -3700,12 +3700,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>0007585-71.2020.8.17.2001</t>
+          <t>0000404-69.2022.8.17.5001</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>0050872-55.2018.8.17.2001</t>
+          <t>0013417-56.2018.8.17.2001</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3736,12 +3736,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>0147878-86.2023.8.17.2001</t>
+          <t>0006011-97.2000.8.17.0001</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3754,12 +3754,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>0013995-77.2022.8.17.2001</t>
+          <t>0000118-91.2022.8.17.5001</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3772,12 +3772,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>0003905-06.2016.8.17.0001</t>
+          <t>0054244-12.2018.8.17.2001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3790,12 +3790,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>0146284-37.2023.8.17.2001</t>
+          <t>0011201-54.2015.8.17.8201</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -3808,12 +3808,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>0112515-38.2023.8.17.2001</t>
+          <t>0053046-17.2025.8.17.8201</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -3826,12 +3826,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>0001891-59.2010.8.17.0001</t>
+          <t>0023117-17.2022.8.17.2001</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>0000787-49.2015.8.17.0650</t>
+          <t>0001619-12.2003.8.17.0001</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -3862,12 +3862,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>0005151-55.2022.8.17.4001</t>
+          <t>0033209-31.2008.8.17.0001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -3880,12 +3880,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0005444-32.2022.8.17.5001</t>
+          <t>0002952-42.2016.8.17.0001</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -3898,12 +3898,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0004217-78.2023.8.17.3220</t>
+          <t>0046975-19.2018.8.17.2001</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0000650-96.2015.8.17.1190</t>
+          <t>0023540-74.2022.8.17.2001</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3934,12 +3934,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0000340-15.2004.8.17.0790</t>
+          <t>0027031-94.2019.8.17.2001</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -3952,12 +3952,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0001962-65.2010.8.17.0420</t>
+          <t>0001413-02.2024.8.17.3480</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -3970,12 +3970,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0000173-14.2024.8.17.3080</t>
+          <t>0018069-17.2024.8.17.3130</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3988,12 +3988,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0000629-03.2024.8.17.2970</t>
+          <t>0001386-20.2021.8.17.5001</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0003043-60.2022.8.17.5001</t>
+          <t>0008804-08.2020.8.17.0001</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0001690-81.2021.8.17.0001</t>
+          <t>0006017-36.2023.8.17.5001</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0005771-10.2020.8.17.0001</t>
+          <t>0000611-97.2024.8.17.5001</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4060,12 +4060,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0013662-58.2015.8.17.0001</t>
+          <t>0159090-41.2022.8.17.2001</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4078,12 +4078,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0000484-20.2022.8.17.2160</t>
+          <t>0011327-03.2014.8.17.0001</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4096,12 +4096,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0006255-05.2023.8.17.3110</t>
+          <t>0071763-87.2024.8.17.2001</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4114,12 +4114,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0000253-86.2019.8.17.3230</t>
+          <t>0017737-86.2017.8.17.2001</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>0002248-61.2024.8.17.2260</t>
+          <t>0124141-20.2024.8.17.2001</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4150,12 +4150,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>0001231-38.2023.8.17.2320</t>
+          <t>0071199-55.2017.8.17.2001</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4168,12 +4168,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>0102850-95.2023.8.17.2001</t>
+          <t>0005403-15.2020.8.17.2001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4186,12 +4186,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>0025886-91.2016.8.17.0001</t>
+          <t>0031288-31.2020.8.17.2001</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>0001899-30.2023.8.17.3380</t>
+          <t>0038337-61.2010.8.17.0001</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4222,12 +4222,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>0001026-03.2024.8.17.3410</t>
+          <t>0141013-13.2024.8.17.2001</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>0001028-70.2024.8.17.3410</t>
+          <t>0000096-35.2020.8.17.1240</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4258,12 +4258,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>0004068-31.2022.8.17.3410</t>
+          <t>0003300-64.2022.8.17.2001</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4276,12 +4276,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>0000014-49.2018.8.17.1280</t>
+          <t>0056247-03.2019.8.17.2001</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4294,12 +4294,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>0002588-48.2015.8.17.1410</t>
+          <t>0003290-20.2022.8.17.2001</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4312,12 +4312,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>0002115-60.2019.8.17.3370</t>
+          <t>0144393-94.2005.8.17.0001</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4330,12 +4330,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>0000238-76.2016.8.17.1370</t>
+          <t>0056243-63.2019.8.17.2001</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>0000720-86.2013.8.17.1060</t>
+          <t>0002530-32.2024.8.17.3220</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4366,12 +4366,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>0000272-27.2003.8.17.0620</t>
+          <t>0000198-49.2021.8.17.3430</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4384,7 +4384,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>0003068-52.2024.8.17.3110</t>
+          <t>0000020-32.2023.8.17.3430</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>0000516-29.2021.8.17.3140</t>
+          <t>0002911-40.2024.8.17.3220</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4420,12 +4420,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>0000610-92.2016.8.17.1380</t>
+          <t>0001126-12.2019.8.17.1250</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4438,12 +4438,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>0000015-72.2020.8.17.3120</t>
+          <t>0000047-49.2022.8.17.3430</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>0000458-95.2016.8.17.1460</t>
+          <t>0000060-48.2022.8.17.3430</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4474,7 +4474,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>0000196-81.2024.8.17.3460</t>
+          <t>0000521-83.2023.8.17.3430</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>0003796-93.2024.8.17.3110</t>
+          <t>0000191-86.2023.8.17.3430</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4510,7 +4510,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>0001193-81.2023.8.17.3110</t>
+          <t>0000244-33.2024.8.17.3430</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4528,7 +4528,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>0000098-79.2013.8.17.1230</t>
+          <t>0000164-34.2017.8.17.3230</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>0000445-65.2022.8.17.3310</t>
+          <t>0000218-41.2023.8.17.3310</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4564,12 +4564,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>0000187-08.2017.8.17.3350</t>
+          <t>0001973-51.2022.8.17.3370</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -4582,12 +4582,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>0000773-83.2024.8.17.2870</t>
+          <t>0004787-65.2024.8.17.3370</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -4600,12 +4600,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>0004278-68.2022.8.17.3350</t>
+          <t>0005922-83.2022.8.17.3370</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -4618,12 +4618,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>0000361-10.2022.8.17.2940</t>
+          <t>0000753-47.2024.8.17.3370</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -4636,12 +4636,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>0001240-89.2024.8.17.2570</t>
+          <t>0000237-39.2017.8.17.3510</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -4654,12 +4654,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>0000866-13.2019.8.17.2970</t>
+          <t>0000250-71.2018.8.17.3520</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -4672,12 +4672,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>0001144-54.2022.8.17.2470</t>
+          <t>0000804-60.2016.8.17.1520</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>0000325-29.2022.8.17.2370</t>
+          <t>0000195-03.2019.8.17.3580</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4708,7 +4708,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>0003292-13.2023.8.17.2370</t>
+          <t>0002723-43.2024.8.17.3480</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4726,12 +4726,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>0000774-68.2024.8.17.2870</t>
+          <t>0001228-77.2021.8.17.3250</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -4744,12 +4744,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>0000195-49.2018.8.17.2800</t>
+          <t>0000288-20.2018.8.17.0340</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>0000770-31.2024.8.17.2870</t>
+          <t>0004068-31.2022.8.17.3410</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -4780,12 +4780,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>0002102-34.2012.8.17.0710</t>
+          <t>0000157-67.2020.8.17.1280</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -4798,12 +4798,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>0000081-12.2016.8.17.0980</t>
+          <t>0000214-60.2024.8.17.3280</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -4816,12 +4816,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>0000661-66.2023.8.17.3350</t>
+          <t>0000800-20.2005.8.17.1290</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -4834,12 +4834,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>0002613-17.2022.8.17.3350</t>
+          <t>0000565-21.2023.8.17.2390</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -4852,12 +4852,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>0001769-09.2018.8.17.3350</t>
+          <t>0000444-67.2024.8.17.2160</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4870,12 +4870,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>0000855-17.2024.8.17.2870</t>
+          <t>0000244-19.2024.8.17.2400</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -4888,12 +4888,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>0004324-44.2023.8.17.2470</t>
+          <t>0000272-62.2023.8.17.2160</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -4906,12 +4906,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>0001454-49.2021.8.17.2970</t>
+          <t>0000200-86.2017.8.17.0640</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>0009789-77.2022.8.17.2370</t>
+          <t>0000485-67.2024.8.17.3410</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -4942,12 +4942,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>0000315-52.2015.8.17.1360</t>
+          <t>0000405-12.2020.8.17.2160</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4960,12 +4960,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>0001289-94.2020.8.17.2110</t>
+          <t>0000654-31.2021.8.17.3290</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>0000006-67.2018.8.17.1120</t>
+          <t>0000592-78.2016.8.17.1410</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -4996,12 +4996,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>0000369-95.2016.8.17.1420</t>
+          <t>0000366-53.2021.8.17.3300</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5014,12 +5014,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>0005241-03.2024.8.17.2220</t>
+          <t>0022974-51.2018.8.17.0810</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>0000052-65.2020.8.17.1450</t>
+          <t>0000886-57.2021.8.17.3350</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5050,12 +5050,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>0004366-72.2023.8.17.3350</t>
+          <t>0000225-03.1995.8.17.0210</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5068,12 +5068,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>0000497-68.2018.8.17.3450</t>
+          <t>0000137-85.2005.8.17.0380</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5086,12 +5086,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>0001105-31.2024.8.17.2650</t>
+          <t>0001642-46.2024.8.17.4810</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>0000004-08.2020.8.17.2970</t>
+          <t>0001375-08.2021.8.17.2150</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5122,12 +5122,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>0000339-30.2004.8.17.0790</t>
+          <t>0000370-56.2022.8.17.3300</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5140,12 +5140,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>0000335-49.2015.8.17.0970</t>
+          <t>0000321-15.2022.8.17.3300</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>0000624-93.2024.8.17.3450</t>
+          <t>0001024-09.2023.8.17.3300</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5176,12 +5176,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>0000264-47.2021.8.17.3230</t>
+          <t>0000271-36.2019.8.17.3480</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>0000027-06.2020.8.17.2500</t>
+          <t>0000018-62.2023.8.17.3430</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5212,12 +5212,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>0000402-92.2013.8.17.0320</t>
+          <t>0000566-10.2015.8.17.1380</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5230,12 +5230,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>0000634-69.2020.8.17.2160</t>
+          <t>0001043-86.2021.8.17.0001</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5248,12 +5248,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>0000818-10.2024.8.17.4480</t>
+          <t>0001506-77.2023.8.17.3260</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5266,12 +5266,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>0000283-18.2023.8.17.4480</t>
+          <t>0006879-06.2022.8.17.3590</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5284,12 +5284,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>0000386-39.2021.8.17.3140</t>
+          <t>0000373-80.2018.8.17.1350</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>0000386-81.2024.8.17.3480</t>
+          <t>0004977-86.2020.8.17.3590</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>0000341-14.2023.8.17.3480</t>
+          <t>0001889-83.2024.8.17.2140</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5338,12 +5338,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>0000038-97.2023.8.17.3480</t>
+          <t>0001861-18.2024.8.17.2140</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>0000335-13.2023.8.17.5030</t>
+          <t>0004657-36.2020.8.17.3590</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5374,12 +5374,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>0001266-10.2023.8.17.3480</t>
+          <t>0006512-78.2014.8.17.0480</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5388,258 +5388,6 @@
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>0000684-87.2024.8.17.3540</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>7ª CC</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>0000638-68.2024.8.17.3550</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>7ª CC</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>0000342-86.2018.8.17.3540</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>7ª CC</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>0000654-50.2018.8.17.3350</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>4ª CCJ</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>0000190-82.2019.8.17.3320</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>0006335-86.2020.8.17.3590</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>0000063-74.2021.8.17.3450</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>0001881-81.2011.8.17.0970</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>4ª CCJ</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>0000206-65.2018.8.17.2190</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>4ª CCJ</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>0001626-51.2024.8.17.2140</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>0000263-34.2021.8.17.2140</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>0001861-18.2024.8.17.2140</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>0000672-05.2024.8.17.2140</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>0001889-83.2024.8.17.2140</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Atualizado com sucesso</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5674,10 +5422,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B2" t="n">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
